--- a/outputs/llm_eval/test_yjx/sig/Critic_correlation_results.xlsx
+++ b/outputs/llm_eval/test_yjx/sig/Critic_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.1982043479741812</v>
+        <v>0.1782487712709642</v>
       </c>
       <c r="C2">
-        <v>0.269628725699655</v>
+        <v>0.1877246197476292</v>
       </c>
       <c r="D2">
-        <v>0.1861940029038673</v>
+        <v>0.1707018313417359</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.3065555806562816</v>
+        <v>0.2933992284343048</v>
       </c>
       <c r="C3">
-        <v>0.3373399960711037</v>
+        <v>0.3440626144089911</v>
       </c>
       <c r="D3">
-        <v>0.2725250275262807</v>
+        <v>0.2711894018509448</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.177142002243319</v>
+        <v>0.223304925248074</v>
       </c>
       <c r="C4">
-        <v>0.2488719504374197</v>
+        <v>0.2409077252303661</v>
       </c>
       <c r="D4">
-        <v>0.1526659613543505</v>
+        <v>0.1971105557865286</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.3760903037080576</v>
+        <v>0.3823795293287333</v>
       </c>
       <c r="C5">
-        <v>0.3886573888111643</v>
+        <v>0.4058516344439491</v>
       </c>
       <c r="D5">
-        <v>0.3189176132854272</v>
+        <v>0.333850366434077</v>
       </c>
     </row>
   </sheetData>
